--- a/production/Purchasing/BOM_Mouser.xlsx
+++ b/production/Purchasing/BOM_Mouser.xlsx
@@ -127,7 +127,7 @@
     <t>1k8</t>
   </si>
   <si>
-    <t>3</t>
+    <t>2</t>
   </si>
   <si>
     <t>RT0402BRD072K2L</t>
